--- a/output/laminas_comunales/comunal_m_saldomigr_a_2020_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_m_saldomigr_a_2020_metropolitana.xlsx
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2019_2020. Escala de colores estandarizada a nivel nacional para todo el periodo.</t>
+          <t>Periodo 2019_2020. Escala comunal recortada a percentiles 3-97. Sobre umbral: San Miguel (5.375); Lampa (5.176); Ñuñoa (3.579). Bajo umbral: Santiago (-7.892); Puente Alto (-5.710); Maipú (-6.806).</t>
         </is>
       </c>
     </row>
